--- a/Development/Common/GameData/StageStartPosition.xlsx
+++ b/Development/Common/GameData/StageStartPosition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EBEAA5-0124-48C2-8398-D78B26D62A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A8ECB3-F7F5-4705-A295-DFC53301F3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="2190" windowWidth="31605" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="2880" windowWidth="31605" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StageStartPosition" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
   <si>
     <t>데이터이름</t>
   </si>
@@ -56,9 +56,6 @@
     <t>DataType</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>DefaultValue</t>
   </si>
   <si>
@@ -134,18 +131,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>double</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>DataTypeDetail</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -187,6 +176,14 @@
   </si>
   <si>
     <t>Yaw</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int32</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -705,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -724,28 +721,28 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="I2" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="96.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -762,7 +759,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -781,25 +778,25 @@
         <v>9</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -807,39 +804,39 @@
         <v>10</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -848,7 +845,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11">
         <v>0</v>
@@ -859,7 +856,7 @@
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G7" s="7">
         <v>0</v>
@@ -876,34 +873,34 @@
     </row>
     <row r="8" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="C8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="9" t="s">
+      <c r="I8" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>46</v>
-      </c>
       <c r="J8" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -911,14 +908,14 @@
         <v>1</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" s="14">
         <v>100</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9" s="14">
         <v>0</v>
@@ -938,16 +935,16 @@
         <v>2</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="14">
         <v>100</v>
       </c>
       <c r="E10" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>18</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>19</v>
       </c>
       <c r="G10" s="14">
         <v>5</v>
@@ -967,14 +964,14 @@
         <v>3</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="14">
         <v>101</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11" s="14">
         <v>0</v>
@@ -994,16 +991,16 @@
         <v>4</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" s="14">
         <v>101</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G12" s="14">
         <v>5</v>
@@ -1023,14 +1020,14 @@
         <v>5</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" s="14">
         <v>102</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G13" s="14">
         <v>0</v>
@@ -1050,14 +1047,14 @@
         <v>6</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="14">
         <v>103</v>
       </c>
       <c r="E14" s="14"/>
       <c r="F14" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14" s="14">
         <v>0</v>

--- a/Development/Common/GameData/StageStartPosition.xlsx
+++ b/Development/Common/GameData/StageStartPosition.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="19.75" customWidth="1" style="12" min="1" max="1"/>
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>25.4943</v>
+        <v>25.116</v>
       </c>
       <c r="I9" t="n">
-        <v>-92</v>
+        <v>-20</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -926,7 +926,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>stage100 Path1</t>
+          <t>stage100 Path1 (레이드 복귀 = 레이드 포탈 앞)</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H10" t="n">
-        <v>25.4943</v>
+        <v>25.116</v>
       </c>
       <c r="I10" t="n">
-        <v>-92</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -1011,6 +1011,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>// 미사용 Stage</t>
+        </is>
+      </c>
       <c r="B13" t="n">
         <v>5</v>
       </c>
@@ -1041,6 +1046,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>// 미사용 Stage</t>
+        </is>
+      </c>
       <c r="B14" t="n">
         <v>6</v>
       </c>
@@ -1071,6 +1081,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>// 미사용 Stage</t>
+        </is>
+      </c>
       <c r="B15" t="n">
         <v>7</v>
       </c>
@@ -1101,6 +1116,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>// 미사용 Stage</t>
+        </is>
+      </c>
       <c r="B16" t="n">
         <v>8</v>
       </c>
@@ -1131,6 +1151,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>// 미사용 Stage</t>
+        </is>
+      </c>
       <c r="B17" t="n">
         <v>9</v>
       </c>
@@ -1161,6 +1186,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>// 미사용 Stage</t>
+        </is>
+      </c>
       <c r="B18" t="n">
         <v>10</v>
       </c>
@@ -1191,6 +1221,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>// 미사용 Stage</t>
+        </is>
+      </c>
       <c r="B19" t="n">
         <v>11</v>
       </c>
@@ -1221,6 +1256,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>// 미사용 Stage</t>
+        </is>
+      </c>
       <c r="B20" t="n">
         <v>12</v>
       </c>
@@ -1251,6 +1291,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>// 미사용 Stage</t>
+        </is>
+      </c>
       <c r="B21" t="n">
         <v>13</v>
       </c>
@@ -1281,6 +1326,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>// 미사용 Stage</t>
+        </is>
+      </c>
       <c r="B22" t="n">
         <v>14</v>
       </c>
@@ -1307,6 +1357,66 @@
         <v>-92</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>stage107 Default</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>107</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-50</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>16</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>stage107 Path1</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>107</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Path1</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-50</v>
+      </c>
+      <c r="J24" t="n">
         <v>0</v>
       </c>
     </row>
